--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -79,49 +79,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ARMAS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>SALINAS</t>
-  </si>
-  <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>JOSE GUSTAVO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>BENJAMIN</t>
-  </si>
-  <si>
-    <t>ARELI CICLARI</t>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>URIEL ARTURO</t>
+  </si>
+  <si>
+    <t>UZIEL</t>
+  </si>
+  <si>
+    <t>ADOLFO</t>
+  </si>
+  <si>
+    <t>LUZ ELENA</t>
   </si>
 </sst>
 </file>
@@ -691,16 +682,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -737,16 +731,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>75.76000000000001</v>
+      </c>
+      <c r="H4">
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -760,16 +757,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>82.61</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -783,16 +783,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>84.20999999999999</v>
+      </c>
+      <c r="H6">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +860,7 @@
         <v>60</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -900,16 +903,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>69.7</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -926,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>78.26000000000001</v>
+        <v>82.61</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -961,7 +964,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1003,16 +1006,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920304</v>
+        <v>24330051920093</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1026,16 +1029,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920147</v>
+        <v>24330051920122</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1049,71 +1052,48 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920400</v>
+        <v>24330051920303</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920188</v>
+        <v>24330051920244</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920217</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,12 @@
     <t>RIOS</t>
   </si>
   <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -97,6 +103,12 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -107,6 +119,12 @@
   </si>
   <si>
     <t>UZIEL</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
   </si>
   <si>
     <t>ADOLFO</t>
@@ -708,16 +726,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>52.94</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -877,16 +898,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>67.65000000000001</v>
+        <v>52.94</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -974,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1012,10 +1033,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1035,10 +1056,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1052,47 +1073,93 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920303</v>
+        <v>24330051920180</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920244</v>
+        <v>24330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24330051920303</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24330051920244</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>ARIAS</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
     <t>HILARIO</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -116,9 +110,6 @@
   </si>
   <si>
     <t>URIEL ARTURO</t>
-  </si>
-  <si>
-    <t>UZIEL</t>
   </si>
   <si>
     <t>MARLENE</t>
@@ -995,7 +986,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1033,10 +1024,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1050,22 +1041,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920122</v>
+        <v>24330051920180</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1073,16 +1064,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920180</v>
+        <v>24330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1096,70 +1087,47 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920190</v>
+        <v>24330051920303</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920303</v>
+        <v>24330051920244</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920244</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,9 @@
     <t>ARIAS</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
     <t>HILARIO</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -110,6 +116,9 @@
   </si>
   <si>
     <t>URIEL ARTURO</t>
+  </si>
+  <si>
+    <t>UZIEL</t>
   </si>
   <si>
     <t>MARLENE</t>
@@ -986,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1024,10 +1033,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1041,22 +1050,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920180</v>
+        <v>24330051920122</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1064,16 +1073,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920190</v>
+        <v>24330051920180</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1087,47 +1096,70 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920303</v>
+        <v>24330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920244</v>
+        <v>24330051920303</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24330051920244</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>11</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="89">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,57 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>DURAN</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
@@ -88,24 +139,72 @@
     <t>HILARIO</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ZOPILLAXTLE</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TLATEMOHUE</t>
+  </si>
+  <si>
+    <t>PAYRO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
@@ -113,6 +212,60 @@
   </si>
   <si>
     <t>TORRES</t>
+  </si>
+  <si>
+    <t>VICTOR YAEL</t>
+  </si>
+  <si>
+    <t>EDWARD ALEXIS</t>
+  </si>
+  <si>
+    <t>EDILBERTO</t>
+  </si>
+  <si>
+    <t>CARLOS ANTONIO</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>SANDY CAMILA</t>
+  </si>
+  <si>
+    <t>AYLIN ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUZ ARIANA</t>
+  </si>
+  <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
+    <t>YARETZY NAOMI</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>ALEYDA MONSERRAT</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>DEREK</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>BENJAMIN</t>
   </si>
   <si>
     <t>URIEL ARTURO</t>
@@ -995,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1027,16 +1180,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920093</v>
+        <v>24330051920092</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1045,21 +1198,21 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920122</v>
+        <v>24330051920156</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1068,98 +1221,512 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920180</v>
+        <v>24330051920410</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920190</v>
+        <v>24330051920143</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920303</v>
+        <v>24330051920400</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920244</v>
+        <v>24330051920213</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>24330051920187</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920201</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920202</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920247</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920283</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920312</v>
+      </c>
+      <c r="B13" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920127</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920147</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920113</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920308</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920355</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920188</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920093</v>
+      </c>
+      <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920122</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920180</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920190</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>24330051920303</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920244</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
         <v>11</v>
       </c>
-      <c r="G7">
+      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -79,211 +79,157 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>APARICIO</t>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>DURAN</t>
   </si>
   <si>
-    <t>PANZO</t>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
   </si>
   <si>
     <t>OSORIO</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>ZENDEJAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>NIETO</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PANIAGUA</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>ZOPILLAXTLE</t>
   </si>
   <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TLATEMOHUE</t>
-  </si>
-  <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
-    <t>VIEYRA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VICTOR YAEL</t>
+    <t>MARIA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ERWIN ISRAEL</t>
+  </si>
+  <si>
+    <t>JESUS DAMIAN</t>
   </si>
   <si>
     <t>EDWARD ALEXIS</t>
   </si>
   <si>
-    <t>EDILBERTO</t>
-  </si>
-  <si>
-    <t>CARLOS ANTONIO</t>
-  </si>
-  <si>
     <t>MARIA MICHELLE</t>
   </si>
   <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
     <t>SANDY CAMILA</t>
   </si>
   <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>IRVING EMILIO</t>
+  </si>
+  <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>SERGIO ALAN</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
     <t>AYLIN ABIGAIL</t>
   </si>
   <si>
+    <t>BENJAMIN</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
     <t>LUZ ARIANA</t>
-  </si>
-  <si>
-    <t>EVAN LAEL</t>
-  </si>
-  <si>
-    <t>YARETZY NAOMI</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>ALEYDA MONSERRAT</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>DEREK</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>BENJAMIN</t>
-  </si>
-  <si>
-    <t>URIEL ARTURO</t>
-  </si>
-  <si>
-    <t>UZIEL</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>ADOLFO</t>
-  </si>
-  <si>
-    <t>LUZ ELENA</t>
   </si>
 </sst>
 </file>
@@ -1025,16 +971,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1077,16 +1023,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>75.76000000000001</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1129,16 +1075,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>84.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -1148,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1180,16 +1126,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920092</v>
+        <v>24330051920104</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1203,16 +1149,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920156</v>
+        <v>24330051920393</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1226,22 +1172,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920410</v>
+        <v>24330051920260</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1249,16 +1195,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920143</v>
+        <v>24330051920156</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1267,7 +1213,7 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1278,10 +1224,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1290,21 +1236,21 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920213</v>
+        <v>24330051920355</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1313,21 +1259,21 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920187</v>
+        <v>24330051920213</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1336,21 +1282,21 @@
         <v>10</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920201</v>
+        <v>24330051920394</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1359,21 +1305,21 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920202</v>
+        <v>24330051920406</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1382,96 +1328,96 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920247</v>
+        <v>24330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920283</v>
+        <v>24330051920409</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920312</v>
+        <v>24330051920258</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920127</v>
+        <v>24330051920405</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -1479,62 +1425,62 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920147</v>
+        <v>24330051920308</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920113</v>
+        <v>24330051920180</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920308</v>
+        <v>24330051920187</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1543,21 +1489,21 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920355</v>
+        <v>24330051920188</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1566,21 +1512,21 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920188</v>
+        <v>24330051920190</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1589,145 +1535,30 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920093</v>
+        <v>24330051920201</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920122</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920180</v>
-      </c>
-      <c r="B22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>24330051920190</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>24330051920303</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>24330051920244</v>
-      </c>
-      <c r="B25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -85,151 +85,52 @@
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>DURAN</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ZENDEJAS</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>NIETO</t>
   </si>
   <si>
     <t>RAMON</t>
   </si>
   <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>VIEYRA</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>SANDOVAL</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PANIAGUA</t>
-  </si>
-  <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>ZOPILLAXTLE</t>
-  </si>
-  <si>
     <t>MARIA ESTEFANIA</t>
   </si>
   <si>
     <t>ERWIN ISRAEL</t>
   </si>
   <si>
+    <t>SAUL</t>
+  </si>
+  <si>
     <t>JESUS DAMIAN</t>
   </si>
   <si>
     <t>EDWARD ALEXIS</t>
   </si>
   <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>SANDY CAMILA</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>IRVING EMILIO</t>
-  </si>
-  <si>
     <t>EVAN LAEL</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>SERGIO ALAN</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>AYLIN ABIGAIL</t>
-  </si>
-  <si>
-    <t>BENJAMIN</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>LUZ ARIANA</t>
   </si>
 </sst>
 </file>
@@ -997,16 +898,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>52.94</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1049,16 +950,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>82.61</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1094,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1132,10 +1033,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1155,10 +1056,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1172,22 +1073,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920260</v>
+        <v>24330051920394</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1195,45 +1096,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920156</v>
+        <v>24330051920260</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920400</v>
+        <v>24330051920156</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1241,16 +1142,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920355</v>
+        <v>24330051920202</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1259,305 +1160,6 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920213</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920394</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920406</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920202</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920409</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920258</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920405</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920308</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920180</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920187</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920188</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920190</v>
-      </c>
-      <c r="B19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920201</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20241.xlsx
@@ -79,55 +79,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DURAN</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DURAN</t>
-  </si>
-  <si>
     <t>ZENDEJAS</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>NIETO</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>NIETO</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
     <t>SANDOVAL</t>
   </si>
   <si>
+    <t>ERWIN ISRAEL</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>JESUS DAMIAN</t>
+  </si>
+  <si>
+    <t>EDWARD ALEXIS</t>
+  </si>
+  <si>
     <t>MARIA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ERWIN ISRAEL</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>JESUS DAMIAN</t>
-  </si>
-  <si>
-    <t>EDWARD ALEXIS</t>
   </si>
   <si>
     <t>EVAN LAEL</t>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920393</v>
+        <v>24330051920394</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1065,7 +1065,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920394</v>
+        <v>24330051920260</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1088,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920260</v>
+        <v>24330051920156</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1111,15 +1111,15 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920156</v>
+        <v>24330051920104</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1160,7 +1160,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
